--- a/4_output/fungi_ASV/fungi_track.xlsx
+++ b/4_output/fungi_ASV/fungi_track.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t>input</t>
   </si>
@@ -302,9 +302,6 @@
     <t>runBE05_FLD0334-r1</t>
   </si>
   <si>
-    <t>runBE08_F10R1-r1</t>
-  </si>
-  <si>
     <t>runBE08_F10R10-r1</t>
   </si>
   <si>
@@ -314,12 +311,6 @@
     <t>runBE08_F10R12-r1</t>
   </si>
   <si>
-    <t>runBE08_F10R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F10R3-r1</t>
-  </si>
-  <si>
     <t>runBE08_F10R4-r1</t>
   </si>
   <si>
@@ -338,24 +329,12 @@
     <t>runBE08_F10R9-r1</t>
   </si>
   <si>
-    <t>runBE08_F11R1-r1</t>
-  </si>
-  <si>
     <t>runBE08_F11R10-r1</t>
   </si>
   <si>
     <t>runBE08_F11R11-r1</t>
   </si>
   <si>
-    <t>runBE08_F11R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F11R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F11R3-r1</t>
-  </si>
-  <si>
     <t>runBE08_F11R4-r1</t>
   </si>
   <si>
@@ -374,24 +353,12 @@
     <t>runBE08_F11R9-r1</t>
   </si>
   <si>
-    <t>runBE08_F12R1-r1</t>
-  </si>
-  <si>
     <t>runBE08_F12R10-r1</t>
   </si>
   <si>
     <t>runBE08_F12R11-r1</t>
   </si>
   <si>
-    <t>runBE08_F12R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F12R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F12R3-r1</t>
-  </si>
-  <si>
     <t>runBE08_F12R4-r1</t>
   </si>
   <si>
@@ -410,162 +377,9 @@
     <t>runBE08_F12R9-r1</t>
   </si>
   <si>
-    <t>runBE08_F13R1-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R4-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R5-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R6-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F13R9-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R1-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R4-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R5-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R6-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F14R9-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R1-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R4-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R5-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R6-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F15R9-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R1-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R4-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R5-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R6-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F16R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F1R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F1R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F1R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F1R12-r1</t>
-  </si>
-  <si>
     <t>runBE08_F1R2-r1</t>
   </si>
   <si>
@@ -584,24 +398,9 @@
     <t>runBE08_F1R7-r1</t>
   </si>
   <si>
-    <t>runBE08_F1R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F1R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F2R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F2R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F2R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F2R12-r1</t>
-  </si>
-  <si>
     <t>runBE08_F2R2-r1</t>
   </si>
   <si>
@@ -620,24 +419,9 @@
     <t>runBE08_F2R7-r1</t>
   </si>
   <si>
-    <t>runBE08_F2R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F2R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F3R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F3R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F3R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F3R12-r1</t>
-  </si>
-  <si>
     <t>runBE08_F3R2-r1</t>
   </si>
   <si>
@@ -653,27 +437,9 @@
     <t>runBE08_F3R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F3R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F3R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F3R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F4R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F4R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F4R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F4R12-r1</t>
-  </si>
-  <si>
     <t>runBE08_F4R2-r1</t>
   </si>
   <si>
@@ -689,24 +455,9 @@
     <t>runBE08_F4R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F4R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F4R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F4R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F5R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F5R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F5R11-r1</t>
-  </si>
-  <si>
     <t>runBE08_F5R12-r1</t>
   </si>
   <si>
@@ -725,126 +476,36 @@
     <t>runBE08_F5R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F5R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F5R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F5R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F6R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F6R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F6R11-r1</t>
-  </si>
-  <si>
     <t>runBE08_F6R12-r1</t>
   </si>
   <si>
-    <t>runBE08_F6R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F6R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F6R4-r1</t>
-  </si>
-  <si>
     <t>runBE08_F6R5-r1</t>
   </si>
   <si>
     <t>runBE08_F6R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F6R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F6R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F6R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F7R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F7R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R4-r1</t>
-  </si>
-  <si>
     <t>runBE08_F7R5-r1</t>
   </si>
   <si>
     <t>runBE08_F7R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F7R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F7R9-r1</t>
-  </si>
-  <si>
     <t>runBE08_F8R1-r1</t>
   </si>
   <si>
-    <t>runBE08_F8R10-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R11-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R12-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R3-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R4-r1</t>
-  </si>
-  <si>
     <t>runBE08_F8R5-r1</t>
   </si>
   <si>
     <t>runBE08_F8R6-r1</t>
   </si>
   <si>
-    <t>runBE08_F8R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F8R9-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F9R1-r1</t>
-  </si>
-  <si>
     <t>runBE08_F9R10-r1</t>
   </si>
   <si>
@@ -854,12 +515,6 @@
     <t>runBE08_F9R12-r1</t>
   </si>
   <si>
-    <t>runBE08_F9R2-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F9R3-r1</t>
-  </si>
-  <si>
     <t>runBE08_F9R4-r1</t>
   </si>
   <si>
@@ -867,15 +522,6 @@
   </si>
   <si>
     <t>runBE08_F9R6-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F9R7-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F9R8-r1</t>
-  </si>
-  <si>
-    <t>runBE08_F9R9-r1</t>
   </si>
 </sst>
 </file>
@@ -2956,16 +2602,16 @@
         <v>25180.0</v>
       </c>
       <c r="D89" t="n">
-        <v>4.0</v>
+        <v>1491.0</v>
       </c>
       <c r="E89" t="n">
-        <v>6.0</v>
+        <v>1507.0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0</v>
+        <v>1371.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>1318.0</v>
       </c>
     </row>
     <row r="90">
@@ -2979,16 +2625,16 @@
         <v>20966.0</v>
       </c>
       <c r="D90" t="n">
-        <v>1485.0</v>
+        <v>10230.0</v>
       </c>
       <c r="E90" t="n">
-        <v>1501.0</v>
+        <v>11634.0</v>
       </c>
       <c r="F90" t="n">
-        <v>1328.0</v>
+        <v>4087.0</v>
       </c>
       <c r="G90" t="n">
-        <v>1292.0</v>
+        <v>3742.0</v>
       </c>
     </row>
     <row r="91">
@@ -3002,16 +2648,16 @@
         <v>18555.0</v>
       </c>
       <c r="D91" t="n">
-        <v>10186.0</v>
+        <v>3043.0</v>
       </c>
       <c r="E91" t="n">
-        <v>11618.0</v>
+        <v>3061.0</v>
       </c>
       <c r="F91" t="n">
-        <v>4059.0</v>
+        <v>2426.0</v>
       </c>
       <c r="G91" t="n">
-        <v>3673.0</v>
+        <v>2324.0</v>
       </c>
     </row>
     <row r="92">
@@ -3019,22 +2665,22 @@
         <v>96</v>
       </c>
       <c r="B92" t="n">
-        <v>188.0</v>
+        <v>2557.0</v>
       </c>
       <c r="C92" t="n">
-        <v>19.0</v>
+        <v>1710.0</v>
       </c>
       <c r="D92" t="n">
-        <v>3068.0</v>
+        <v>2742.0</v>
       </c>
       <c r="E92" t="n">
-        <v>3084.0</v>
+        <v>2796.0</v>
       </c>
       <c r="F92" t="n">
-        <v>2381.0</v>
+        <v>2314.0</v>
       </c>
       <c r="G92" t="n">
-        <v>2264.0</v>
+        <v>2239.0</v>
       </c>
     </row>
     <row r="93">
@@ -3042,22 +2688,22 @@
         <v>97</v>
       </c>
       <c r="B93" t="n">
-        <v>2557.0</v>
+        <v>15174.0</v>
       </c>
       <c r="C93" t="n">
-        <v>1710.0</v>
+        <v>12397.0</v>
       </c>
       <c r="D93" t="n">
-        <v>1.0</v>
+        <v>2642.0</v>
       </c>
       <c r="E93" t="n">
-        <v>1.0</v>
+        <v>2811.0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0</v>
+        <v>2005.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>1963.0</v>
       </c>
     </row>
     <row r="94">
@@ -3065,22 +2711,22 @@
         <v>98</v>
       </c>
       <c r="B94" t="n">
-        <v>15174.0</v>
+        <v>3469.0</v>
       </c>
       <c r="C94" t="n">
-        <v>12397.0</v>
+        <v>3112.0</v>
       </c>
       <c r="D94" t="n">
-        <v>1.0</v>
+        <v>736.0</v>
       </c>
       <c r="E94" t="n">
-        <v>1.0</v>
+        <v>778.0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>653.0</v>
       </c>
     </row>
     <row r="95">
@@ -3088,22 +2734,22 @@
         <v>99</v>
       </c>
       <c r="B95" t="n">
-        <v>3469.0</v>
+        <v>3963.0</v>
       </c>
       <c r="C95" t="n">
-        <v>3112.0</v>
+        <v>3420.0</v>
       </c>
       <c r="D95" t="n">
-        <v>2734.0</v>
+        <v>2470.0</v>
       </c>
       <c r="E95" t="n">
-        <v>2777.0</v>
+        <v>2552.0</v>
       </c>
       <c r="F95" t="n">
-        <v>2242.0</v>
+        <v>2072.0</v>
       </c>
       <c r="G95" t="n">
-        <v>2127.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="96">
@@ -3111,19 +2757,19 @@
         <v>100</v>
       </c>
       <c r="B96" t="n">
-        <v>150.0</v>
+        <v>4003.0</v>
       </c>
       <c r="C96" t="n">
-        <v>8.0</v>
+        <v>3447.0</v>
       </c>
       <c r="D96" t="n">
-        <v>2604.0</v>
+        <v>2425.0</v>
       </c>
       <c r="E96" t="n">
-        <v>2796.0</v>
+        <v>2442.0</v>
       </c>
       <c r="F96" t="n">
-        <v>1956.0</v>
+        <v>2032.0</v>
       </c>
       <c r="G96" t="n">
         <v>1886.0</v>
@@ -3134,22 +2780,22 @@
         <v>101</v>
       </c>
       <c r="B97" t="n">
-        <v>157.0</v>
+        <v>1295.0</v>
       </c>
       <c r="C97" t="n">
-        <v>29.0</v>
+        <v>847.0</v>
       </c>
       <c r="D97" t="n">
-        <v>747.0</v>
+        <v>1018.0</v>
       </c>
       <c r="E97" t="n">
-        <v>764.0</v>
+        <v>1027.0</v>
       </c>
       <c r="F97" t="n">
-        <v>691.0</v>
+        <v>870.0</v>
       </c>
       <c r="G97" t="n">
-        <v>644.0</v>
+        <v>870.0</v>
       </c>
     </row>
     <row r="98">
@@ -3157,22 +2803,22 @@
         <v>102</v>
       </c>
       <c r="B98" t="n">
-        <v>3963.0</v>
+        <v>3595.0</v>
       </c>
       <c r="C98" t="n">
-        <v>3420.0</v>
+        <v>3124.0</v>
       </c>
       <c r="D98" t="n">
-        <v>2444.0</v>
+        <v>927.0</v>
       </c>
       <c r="E98" t="n">
-        <v>2546.0</v>
+        <v>929.0</v>
       </c>
       <c r="F98" t="n">
-        <v>2050.0</v>
+        <v>793.0</v>
       </c>
       <c r="G98" t="n">
-        <v>1990.0</v>
+        <v>769.0</v>
       </c>
     </row>
     <row r="99">
@@ -3180,22 +2826,22 @@
         <v>103</v>
       </c>
       <c r="B99" t="n">
-        <v>4003.0</v>
+        <v>3082.0</v>
       </c>
       <c r="C99" t="n">
-        <v>3447.0</v>
+        <v>2771.0</v>
       </c>
       <c r="D99" t="n">
-        <v>2384.0</v>
+        <v>9015.0</v>
       </c>
       <c r="E99" t="n">
-        <v>2429.0</v>
+        <v>10072.0</v>
       </c>
       <c r="F99" t="n">
-        <v>1980.0</v>
+        <v>3629.0</v>
       </c>
       <c r="G99" t="n">
-        <v>1812.0</v>
+        <v>3373.0</v>
       </c>
     </row>
     <row r="100">
@@ -3203,22 +2849,22 @@
         <v>104</v>
       </c>
       <c r="B100" t="n">
-        <v>1295.0</v>
+        <v>2555.0</v>
       </c>
       <c r="C100" t="n">
-        <v>847.0</v>
+        <v>1177.0</v>
       </c>
       <c r="D100" t="n">
-        <v>997.0</v>
+        <v>3065.0</v>
       </c>
       <c r="E100" t="n">
-        <v>1040.0</v>
+        <v>3122.0</v>
       </c>
       <c r="F100" t="n">
-        <v>874.0</v>
+        <v>2642.0</v>
       </c>
       <c r="G100" t="n">
-        <v>874.0</v>
+        <v>2613.0</v>
       </c>
     </row>
     <row r="101">
@@ -3226,22 +2872,22 @@
         <v>105</v>
       </c>
       <c r="B101" t="n">
-        <v>3595.0</v>
+        <v>2643.0</v>
       </c>
       <c r="C101" t="n">
-        <v>3124.0</v>
+        <v>1116.0</v>
       </c>
       <c r="D101" t="n">
-        <v>5.0</v>
+        <v>3253.0</v>
       </c>
       <c r="E101" t="n">
-        <v>5.0</v>
+        <v>3447.0</v>
       </c>
       <c r="F101" t="n">
-        <v>5.0</v>
+        <v>2657.0</v>
       </c>
       <c r="G101" t="n">
-        <v>5.0</v>
+        <v>2580.0</v>
       </c>
     </row>
     <row r="102">
@@ -3249,22 +2895,22 @@
         <v>106</v>
       </c>
       <c r="B102" t="n">
-        <v>3082.0</v>
+        <v>12455.0</v>
       </c>
       <c r="C102" t="n">
-        <v>2771.0</v>
+        <v>10904.0</v>
       </c>
       <c r="D102" t="n">
-        <v>919.0</v>
+        <v>2867.0</v>
       </c>
       <c r="E102" t="n">
-        <v>931.0</v>
+        <v>2939.0</v>
       </c>
       <c r="F102" t="n">
-        <v>796.0</v>
+        <v>2474.0</v>
       </c>
       <c r="G102" t="n">
-        <v>775.0</v>
+        <v>2245.0</v>
       </c>
     </row>
     <row r="103">
@@ -3272,22 +2918,22 @@
         <v>107</v>
       </c>
       <c r="B103" t="n">
-        <v>2555.0</v>
+        <v>4289.0</v>
       </c>
       <c r="C103" t="n">
-        <v>1177.0</v>
+        <v>3811.0</v>
       </c>
       <c r="D103" t="n">
-        <v>8986.0</v>
+        <v>3050.0</v>
       </c>
       <c r="E103" t="n">
-        <v>10084.0</v>
+        <v>3091.0</v>
       </c>
       <c r="F103" t="n">
-        <v>3560.0</v>
+        <v>2497.0</v>
       </c>
       <c r="G103" t="n">
-        <v>3281.0</v>
+        <v>2462.0</v>
       </c>
     </row>
     <row r="104">
@@ -3295,22 +2941,22 @@
         <v>108</v>
       </c>
       <c r="B104" t="n">
-        <v>33.0</v>
+        <v>4558.0</v>
       </c>
       <c r="C104" t="n">
-        <v>16.0</v>
+        <v>4078.0</v>
       </c>
       <c r="D104" t="n">
-        <v>2.0</v>
+        <v>3042.0</v>
       </c>
       <c r="E104" t="n">
-        <v>2.0</v>
+        <v>3088.0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0</v>
+        <v>2547.0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0</v>
+        <v>2406.0</v>
       </c>
     </row>
     <row r="105">
@@ -3318,22 +2964,22 @@
         <v>109</v>
       </c>
       <c r="B105" t="n">
-        <v>2643.0</v>
+        <v>3826.0</v>
       </c>
       <c r="C105" t="n">
-        <v>1116.0</v>
+        <v>3269.0</v>
       </c>
       <c r="D105" t="n">
-        <v>1.0</v>
+        <v>1409.0</v>
       </c>
       <c r="E105" t="n">
-        <v>1.0</v>
+        <v>1420.0</v>
       </c>
       <c r="F105" t="n">
-        <v>1.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G105" t="n">
-        <v>1.0</v>
+        <v>1164.0</v>
       </c>
     </row>
     <row r="106">
@@ -3341,22 +2987,22 @@
         <v>110</v>
       </c>
       <c r="B106" t="n">
-        <v>12455.0</v>
+        <v>4168.0</v>
       </c>
       <c r="C106" t="n">
-        <v>10904.0</v>
+        <v>3723.0</v>
       </c>
       <c r="D106" t="n">
-        <v>10.0</v>
+        <v>1148.0</v>
       </c>
       <c r="E106" t="n">
-        <v>10.0</v>
+        <v>1173.0</v>
       </c>
       <c r="F106" t="n">
-        <v>10.0</v>
+        <v>1043.0</v>
       </c>
       <c r="G106" t="n">
-        <v>10.0</v>
+        <v>984.0</v>
       </c>
     </row>
     <row r="107">
@@ -3364,22 +3010,22 @@
         <v>111</v>
       </c>
       <c r="B107" t="n">
-        <v>25.0</v>
+        <v>3970.0</v>
       </c>
       <c r="C107" t="n">
-        <v>6.0</v>
+        <v>3552.0</v>
       </c>
       <c r="D107" t="n">
-        <v>3023.0</v>
+        <v>6485.0</v>
       </c>
       <c r="E107" t="n">
-        <v>3082.0</v>
+        <v>7327.0</v>
       </c>
       <c r="F107" t="n">
-        <v>2565.0</v>
+        <v>2561.0</v>
       </c>
       <c r="G107" t="n">
-        <v>2532.0</v>
+        <v>2370.0</v>
       </c>
     </row>
     <row r="108">
@@ -3387,22 +3033,22 @@
         <v>112</v>
       </c>
       <c r="B108" t="n">
-        <v>94.0</v>
+        <v>2931.0</v>
       </c>
       <c r="C108" t="n">
-        <v>2.0</v>
+        <v>1648.0</v>
       </c>
       <c r="D108" t="n">
-        <v>3247.0</v>
+        <v>3170.0</v>
       </c>
       <c r="E108" t="n">
-        <v>3464.0</v>
+        <v>3270.0</v>
       </c>
       <c r="F108" t="n">
-        <v>2640.0</v>
+        <v>2652.0</v>
       </c>
       <c r="G108" t="n">
-        <v>2563.0</v>
+        <v>2584.0</v>
       </c>
     </row>
     <row r="109">
@@ -3410,22 +3056,22 @@
         <v>113</v>
       </c>
       <c r="B109" t="n">
-        <v>73.0</v>
+        <v>1732.0</v>
       </c>
       <c r="C109" t="n">
-        <v>30.0</v>
+        <v>1295.0</v>
       </c>
       <c r="D109" t="n">
-        <v>2888.0</v>
+        <v>1622.0</v>
       </c>
       <c r="E109" t="n">
-        <v>2924.0</v>
+        <v>1631.0</v>
       </c>
       <c r="F109" t="n">
-        <v>2413.0</v>
+        <v>1320.0</v>
       </c>
       <c r="G109" t="n">
-        <v>2163.0</v>
+        <v>1275.0</v>
       </c>
     </row>
     <row r="110">
@@ -3433,22 +3079,22 @@
         <v>114</v>
       </c>
       <c r="B110" t="n">
-        <v>4289.0</v>
+        <v>11146.0</v>
       </c>
       <c r="C110" t="n">
-        <v>3811.0</v>
+        <v>8240.0</v>
       </c>
       <c r="D110" t="n">
-        <v>3054.0</v>
+        <v>3368.0</v>
       </c>
       <c r="E110" t="n">
-        <v>3082.0</v>
+        <v>3458.0</v>
       </c>
       <c r="F110" t="n">
-        <v>2429.0</v>
+        <v>3085.0</v>
       </c>
       <c r="G110" t="n">
-        <v>2405.0</v>
+        <v>2809.0</v>
       </c>
     </row>
     <row r="111">
@@ -3456,22 +3102,22 @@
         <v>115</v>
       </c>
       <c r="B111" t="n">
-        <v>4558.0</v>
+        <v>4314.0</v>
       </c>
       <c r="C111" t="n">
-        <v>4078.0</v>
+        <v>3852.0</v>
       </c>
       <c r="D111" t="n">
-        <v>3008.0</v>
+        <v>3787.0</v>
       </c>
       <c r="E111" t="n">
-        <v>3079.0</v>
+        <v>3859.0</v>
       </c>
       <c r="F111" t="n">
-        <v>2501.0</v>
+        <v>3292.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2352.0</v>
+        <v>3132.0</v>
       </c>
     </row>
     <row r="112">
@@ -3479,22 +3125,22 @@
         <v>116</v>
       </c>
       <c r="B112" t="n">
-        <v>3826.0</v>
+        <v>2962.0</v>
       </c>
       <c r="C112" t="n">
-        <v>3269.0</v>
+        <v>2027.0</v>
       </c>
       <c r="D112" t="n">
-        <v>1401.0</v>
+        <v>2487.0</v>
       </c>
       <c r="E112" t="n">
-        <v>1421.0</v>
+        <v>2487.0</v>
       </c>
       <c r="F112" t="n">
-        <v>1197.0</v>
+        <v>2163.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1171.0</v>
+        <v>2115.0</v>
       </c>
     </row>
     <row r="113">
@@ -3502,22 +3148,22 @@
         <v>117</v>
       </c>
       <c r="B113" t="n">
-        <v>4168.0</v>
+        <v>4103.0</v>
       </c>
       <c r="C113" t="n">
-        <v>3723.0</v>
+        <v>3685.0</v>
       </c>
       <c r="D113" t="n">
-        <v>1.0</v>
+        <v>2024.0</v>
       </c>
       <c r="E113" t="n">
-        <v>1.0</v>
+        <v>2101.0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0</v>
+        <v>1839.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>1749.0</v>
       </c>
     </row>
     <row r="114">
@@ -3525,22 +3171,22 @@
         <v>118</v>
       </c>
       <c r="B114" t="n">
-        <v>3970.0</v>
+        <v>5027.0</v>
       </c>
       <c r="C114" t="n">
-        <v>3552.0</v>
+        <v>4458.0</v>
       </c>
       <c r="D114" t="n">
-        <v>1146.0</v>
+        <v>2771.0</v>
       </c>
       <c r="E114" t="n">
-        <v>1173.0</v>
+        <v>2838.0</v>
       </c>
       <c r="F114" t="n">
-        <v>1034.0</v>
+        <v>2214.0</v>
       </c>
       <c r="G114" t="n">
-        <v>987.0</v>
+        <v>2188.0</v>
       </c>
     </row>
     <row r="115">
@@ -3548,22 +3194,22 @@
         <v>119</v>
       </c>
       <c r="B115" t="n">
-        <v>2931.0</v>
+        <v>3344.0</v>
       </c>
       <c r="C115" t="n">
-        <v>1648.0</v>
+        <v>3001.0</v>
       </c>
       <c r="D115" t="n">
-        <v>6505.0</v>
+        <v>3641.0</v>
       </c>
       <c r="E115" t="n">
-        <v>7341.0</v>
+        <v>3663.0</v>
       </c>
       <c r="F115" t="n">
-        <v>2550.0</v>
+        <v>3118.0</v>
       </c>
       <c r="G115" t="n">
-        <v>2346.0</v>
+        <v>2986.0</v>
       </c>
     </row>
     <row r="116">
@@ -3571,22 +3217,22 @@
         <v>120</v>
       </c>
       <c r="B116" t="n">
-        <v>88.0</v>
+        <v>3371.0</v>
       </c>
       <c r="C116" t="n">
-        <v>17.0</v>
+        <v>2318.0</v>
       </c>
       <c r="D116" t="n">
-        <v>2.0</v>
+        <v>2999.0</v>
       </c>
       <c r="E116" t="n">
-        <v>2.0</v>
+        <v>3056.0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0</v>
+        <v>2404.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="117">
@@ -3594,22 +3240,22 @@
         <v>121</v>
       </c>
       <c r="B117" t="n">
-        <v>1732.0</v>
+        <v>3781.0</v>
       </c>
       <c r="C117" t="n">
-        <v>1295.0</v>
+        <v>3357.0</v>
       </c>
       <c r="D117" t="n">
-        <v>1.0</v>
+        <v>862.0</v>
       </c>
       <c r="E117" t="n">
-        <v>1.0</v>
+        <v>911.0</v>
       </c>
       <c r="F117" t="n">
-        <v>1.0</v>
+        <v>710.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>685.0</v>
       </c>
     </row>
     <row r="118">
@@ -3617,22 +3263,22 @@
         <v>122</v>
       </c>
       <c r="B118" t="n">
-        <v>11146.0</v>
+        <v>4753.0</v>
       </c>
       <c r="C118" t="n">
-        <v>8240.0</v>
+        <v>4218.0</v>
       </c>
       <c r="D118" t="n">
-        <v>2.0</v>
+        <v>648.0</v>
       </c>
       <c r="E118" t="n">
-        <v>2.0</v>
+        <v>650.0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0</v>
+        <v>522.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>500.0</v>
       </c>
     </row>
     <row r="119">
@@ -3640,22 +3286,22 @@
         <v>123</v>
       </c>
       <c r="B119" t="n">
-        <v>41.0</v>
+        <v>4210.0</v>
       </c>
       <c r="C119" t="n">
-        <v>11.0</v>
+        <v>3723.0</v>
       </c>
       <c r="D119" t="n">
-        <v>3155.0</v>
+        <v>3244.0</v>
       </c>
       <c r="E119" t="n">
-        <v>3286.0</v>
+        <v>3332.0</v>
       </c>
       <c r="F119" t="n">
-        <v>2650.0</v>
+        <v>2926.0</v>
       </c>
       <c r="G119" t="n">
-        <v>2552.0</v>
+        <v>2723.0</v>
       </c>
     </row>
     <row r="120">
@@ -3663,22 +3309,22 @@
         <v>124</v>
       </c>
       <c r="B120" t="n">
-        <v>75.0</v>
+        <v>2758.0</v>
       </c>
       <c r="C120" t="n">
-        <v>2.0</v>
+        <v>1109.0</v>
       </c>
       <c r="D120" t="n">
-        <v>1636.0</v>
+        <v>18.0</v>
       </c>
       <c r="E120" t="n">
-        <v>1637.0</v>
+        <v>5.0</v>
       </c>
       <c r="F120" t="n">
-        <v>1303.0</v>
+        <v>4.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1245.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="121">
@@ -3686,22 +3332,22 @@
         <v>125</v>
       </c>
       <c r="B121" t="n">
-        <v>79.0</v>
+        <v>2382.0</v>
       </c>
       <c r="C121" t="n">
-        <v>23.0</v>
+        <v>818.0</v>
       </c>
       <c r="D121" t="n">
-        <v>3321.0</v>
+        <v>2449.0</v>
       </c>
       <c r="E121" t="n">
-        <v>3482.0</v>
+        <v>2559.0</v>
       </c>
       <c r="F121" t="n">
-        <v>3010.0</v>
+        <v>2119.0</v>
       </c>
       <c r="G121" t="n">
-        <v>2732.0</v>
+        <v>2052.0</v>
       </c>
     </row>
     <row r="122">
@@ -3709,22 +3355,22 @@
         <v>126</v>
       </c>
       <c r="B122" t="n">
-        <v>4314.0</v>
+        <v>4005.0</v>
       </c>
       <c r="C122" t="n">
-        <v>3852.0</v>
+        <v>3590.0</v>
       </c>
       <c r="D122" t="n">
-        <v>3769.0</v>
+        <v>4096.0</v>
       </c>
       <c r="E122" t="n">
-        <v>3870.0</v>
+        <v>4207.0</v>
       </c>
       <c r="F122" t="n">
-        <v>3230.0</v>
+        <v>3644.0</v>
       </c>
       <c r="G122" t="n">
-        <v>3070.0</v>
+        <v>3358.0</v>
       </c>
     </row>
     <row r="123">
@@ -3732,22 +3378,22 @@
         <v>127</v>
       </c>
       <c r="B123" t="n">
-        <v>2962.0</v>
+        <v>106.0</v>
       </c>
       <c r="C123" t="n">
-        <v>2027.0</v>
+        <v>63.0</v>
       </c>
       <c r="D123" t="n">
-        <v>2439.0</v>
+        <v>2694.0</v>
       </c>
       <c r="E123" t="n">
-        <v>2488.0</v>
+        <v>2758.0</v>
       </c>
       <c r="F123" t="n">
-        <v>2108.0</v>
+        <v>2251.0</v>
       </c>
       <c r="G123" t="n">
-        <v>2060.0</v>
+        <v>2194.0</v>
       </c>
     </row>
     <row r="124">
@@ -3755,22 +3401,22 @@
         <v>128</v>
       </c>
       <c r="B124" t="n">
-        <v>4103.0</v>
+        <v>3577.0</v>
       </c>
       <c r="C124" t="n">
-        <v>3685.0</v>
+        <v>3125.0</v>
       </c>
       <c r="D124" t="n">
-        <v>2004.0</v>
+        <v>2275.0</v>
       </c>
       <c r="E124" t="n">
-        <v>2068.0</v>
+        <v>2258.0</v>
       </c>
       <c r="F124" t="n">
-        <v>1790.0</v>
+        <v>1883.0</v>
       </c>
       <c r="G124" t="n">
-        <v>1688.0</v>
+        <v>1791.0</v>
       </c>
     </row>
     <row r="125">
@@ -3778,22 +3424,22 @@
         <v>129</v>
       </c>
       <c r="B125" t="n">
-        <v>5027.0</v>
+        <v>4985.0</v>
       </c>
       <c r="C125" t="n">
-        <v>4458.0</v>
+        <v>4550.0</v>
       </c>
       <c r="D125" t="n">
-        <v>5.0</v>
+        <v>1184.0</v>
       </c>
       <c r="E125" t="n">
-        <v>3.0</v>
+        <v>1207.0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0</v>
+        <v>1013.0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0</v>
+        <v>996.0</v>
       </c>
     </row>
     <row r="126">
@@ -3801,22 +3447,22 @@
         <v>130</v>
       </c>
       <c r="B126" t="n">
-        <v>3344.0</v>
+        <v>3945.0</v>
       </c>
       <c r="C126" t="n">
-        <v>3001.0</v>
+        <v>3384.0</v>
       </c>
       <c r="D126" t="n">
-        <v>1.0</v>
+        <v>2827.0</v>
       </c>
       <c r="E126" t="n">
-        <v>1.0</v>
+        <v>2862.0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0</v>
+        <v>1972.0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0</v>
+        <v>1857.0</v>
       </c>
     </row>
     <row r="127">
@@ -3824,22 +3470,22 @@
         <v>131</v>
       </c>
       <c r="B127" t="n">
-        <v>3371.0</v>
+        <v>3232.0</v>
       </c>
       <c r="C127" t="n">
-        <v>2318.0</v>
+        <v>2631.0</v>
       </c>
       <c r="D127" t="n">
-        <v>2744.0</v>
+        <v>2614.0</v>
       </c>
       <c r="E127" t="n">
-        <v>3612.0</v>
+        <v>2613.0</v>
       </c>
       <c r="F127" t="n">
-        <v>283.0</v>
+        <v>2125.0</v>
       </c>
       <c r="G127" t="n">
-        <v>268.0</v>
+        <v>2102.0</v>
       </c>
     </row>
     <row r="128">
@@ -3847,22 +3493,22 @@
         <v>132</v>
       </c>
       <c r="B128" t="n">
-        <v>38.0</v>
+        <v>2806.0</v>
       </c>
       <c r="C128" t="n">
-        <v>8.0</v>
+        <v>1452.0</v>
       </c>
       <c r="D128" t="n">
-        <v>1.0</v>
+        <v>2413.0</v>
       </c>
       <c r="E128" t="n">
-        <v>1.0</v>
+        <v>2501.0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0</v>
+        <v>2001.0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0</v>
+        <v>1942.0</v>
       </c>
     </row>
     <row r="129">
@@ -3870,22 +3516,22 @@
         <v>133</v>
       </c>
       <c r="B129" t="n">
-        <v>8.0</v>
+        <v>3692.0</v>
       </c>
       <c r="C129" t="n">
-        <v>2.0</v>
+        <v>3209.0</v>
       </c>
       <c r="D129" t="n">
-        <v>1.0</v>
+        <v>2879.0</v>
       </c>
       <c r="E129" t="n">
-        <v>1.0</v>
+        <v>2861.0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0</v>
+        <v>2409.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>2306.0</v>
       </c>
     </row>
     <row r="130">
@@ -3893,22 +3539,22 @@
         <v>134</v>
       </c>
       <c r="B130" t="n">
-        <v>6483.0</v>
+        <v>3919.0</v>
       </c>
       <c r="C130" t="n">
-        <v>4091.0</v>
+        <v>3266.0</v>
       </c>
       <c r="D130" t="n">
-        <v>1.0</v>
+        <v>2876.0</v>
       </c>
       <c r="E130" t="n">
-        <v>1.0</v>
+        <v>2970.0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0</v>
+        <v>2408.0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="131">
@@ -3916,22 +3562,22 @@
         <v>135</v>
       </c>
       <c r="B131" t="n">
-        <v>21.0</v>
+        <v>3465.0</v>
       </c>
       <c r="C131" t="n">
-        <v>4.0</v>
+        <v>3068.0</v>
       </c>
       <c r="D131" t="n">
-        <v>2.0</v>
+        <v>2496.0</v>
       </c>
       <c r="E131" t="n">
-        <v>2.0</v>
+        <v>2609.0</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0</v>
+        <v>2084.0</v>
       </c>
       <c r="G131" t="n">
-        <v>2.0</v>
+        <v>2070.0</v>
       </c>
     </row>
     <row r="132">
@@ -3939,22 +3585,22 @@
         <v>136</v>
       </c>
       <c r="B132" t="n">
-        <v>35.0</v>
+        <v>3872.0</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0</v>
+        <v>3407.0</v>
       </c>
       <c r="D132" t="n">
-        <v>2.0</v>
+        <v>1171.0</v>
       </c>
       <c r="E132" t="n">
-        <v>1.0</v>
+        <v>1196.0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0</v>
+        <v>1012.0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0</v>
+        <v>1012.0</v>
       </c>
     </row>
     <row r="133">
@@ -3962,22 +3608,22 @@
         <v>137</v>
       </c>
       <c r="B133" t="n">
-        <v>55.0</v>
+        <v>3911.0</v>
       </c>
       <c r="C133" t="n">
-        <v>11.0</v>
+        <v>3482.0</v>
       </c>
       <c r="D133" t="n">
-        <v>2.0</v>
+        <v>2595.0</v>
       </c>
       <c r="E133" t="n">
-        <v>32.0</v>
+        <v>2688.0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0</v>
+        <v>2290.0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0</v>
+        <v>2114.0</v>
       </c>
     </row>
     <row r="134">
@@ -3985,22 +3631,22 @@
         <v>138</v>
       </c>
       <c r="B134" t="n">
-        <v>34.0</v>
+        <v>3656.0</v>
       </c>
       <c r="C134" t="n">
-        <v>2.0</v>
+        <v>3155.0</v>
       </c>
       <c r="D134" t="n">
-        <v>1.0</v>
+        <v>2425.0</v>
       </c>
       <c r="E134" t="n">
-        <v>1.0</v>
+        <v>2518.0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0</v>
+        <v>1994.0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0</v>
+        <v>1977.0</v>
       </c>
     </row>
     <row r="135">
@@ -4008,22 +3654,22 @@
         <v>139</v>
       </c>
       <c r="B135" t="n">
-        <v>14.0</v>
+        <v>2387.0</v>
       </c>
       <c r="C135" t="n">
-        <v>4.0</v>
+        <v>1386.0</v>
       </c>
       <c r="D135" t="n">
-        <v>1.0</v>
+        <v>2808.0</v>
       </c>
       <c r="E135" t="n">
-        <v>1.0</v>
+        <v>2831.0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0</v>
+        <v>2264.0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0</v>
+        <v>2236.0</v>
       </c>
     </row>
     <row r="136">
@@ -4031,22 +3677,22 @@
         <v>140</v>
       </c>
       <c r="B136" t="n">
-        <v>14.0</v>
+        <v>3534.0</v>
       </c>
       <c r="C136" t="n">
-        <v>9.0</v>
+        <v>2992.0</v>
       </c>
       <c r="D136" t="n">
-        <v>1.0</v>
+        <v>3232.0</v>
       </c>
       <c r="E136" t="n">
-        <v>1.0</v>
+        <v>3401.0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0</v>
+        <v>2677.0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0</v>
+        <v>2583.0</v>
       </c>
     </row>
     <row r="137">
@@ -4054,22 +3700,22 @@
         <v>141</v>
       </c>
       <c r="B137" t="n">
-        <v>64.0</v>
+        <v>3529.0</v>
       </c>
       <c r="C137" t="n">
-        <v>35.0</v>
+        <v>3108.0</v>
       </c>
       <c r="D137" t="n">
-        <v>2622.0</v>
+        <v>781.0</v>
       </c>
       <c r="E137" t="n">
-        <v>3410.0</v>
+        <v>801.0</v>
       </c>
       <c r="F137" t="n">
-        <v>114.0</v>
+        <v>743.0</v>
       </c>
       <c r="G137" t="n">
-        <v>99.0</v>
+        <v>743.0</v>
       </c>
     </row>
     <row r="138">
@@ -4077,22 +3723,22 @@
         <v>142</v>
       </c>
       <c r="B138" t="n">
-        <v>2.0</v>
+        <v>3840.0</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0</v>
+        <v>3385.0</v>
       </c>
       <c r="D138" t="n">
-        <v>2.0</v>
+        <v>1050.0</v>
       </c>
       <c r="E138" t="n">
-        <v>2.0</v>
+        <v>1036.0</v>
       </c>
       <c r="F138" t="n">
-        <v>2.0</v>
+        <v>905.0</v>
       </c>
       <c r="G138" t="n">
-        <v>2.0</v>
+        <v>886.0</v>
       </c>
     </row>
     <row r="139">
@@ -4100,22 +3746,22 @@
         <v>143</v>
       </c>
       <c r="B139" t="n">
-        <v>22.0</v>
+        <v>4514.0</v>
       </c>
       <c r="C139" t="n">
-        <v>6.0</v>
+        <v>4005.0</v>
       </c>
       <c r="D139" t="n">
-        <v>1.0</v>
+        <v>3352.0</v>
       </c>
       <c r="E139" t="n">
-        <v>1.0</v>
+        <v>3480.0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0</v>
+        <v>2928.0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0</v>
+        <v>2749.0</v>
       </c>
     </row>
     <row r="140">
@@ -4123,22 +3769,22 @@
         <v>144</v>
       </c>
       <c r="B140" t="n">
-        <v>21.0</v>
+        <v>2604.0</v>
       </c>
       <c r="C140" t="n">
-        <v>4.0</v>
+        <v>932.0</v>
       </c>
       <c r="D140" t="n">
-        <v>1.0</v>
+        <v>2502.0</v>
       </c>
       <c r="E140" t="n">
-        <v>1.0</v>
+        <v>2602.0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0</v>
+        <v>1957.0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0</v>
+        <v>1902.0</v>
       </c>
     </row>
     <row r="141">
@@ -4146,22 +3792,22 @@
         <v>145</v>
       </c>
       <c r="B141" t="n">
-        <v>14.0</v>
+        <v>2475.0</v>
       </c>
       <c r="C141" t="n">
-        <v>5.0</v>
+        <v>1250.0</v>
       </c>
       <c r="D141" t="n">
-        <v>1.0</v>
+        <v>26.0</v>
       </c>
       <c r="E141" t="n">
-        <v>1.0</v>
+        <v>27.0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="142">
@@ -4169,22 +3815,22 @@
         <v>146</v>
       </c>
       <c r="B142" t="n">
-        <v>5633.0</v>
+        <v>4021.0</v>
       </c>
       <c r="C142" t="n">
-        <v>3724.0</v>
+        <v>3660.0</v>
       </c>
       <c r="D142" t="n">
-        <v>1.0</v>
+        <v>2512.0</v>
       </c>
       <c r="E142" t="n">
-        <v>2.0</v>
+        <v>2558.0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0</v>
+        <v>2163.0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0</v>
+        <v>2129.0</v>
       </c>
     </row>
     <row r="143">
@@ -4192,22 +3838,22 @@
         <v>147</v>
       </c>
       <c r="B143" t="n">
-        <v>11.0</v>
+        <v>3586.0</v>
       </c>
       <c r="C143" t="n">
-        <v>4.0</v>
+        <v>3076.0</v>
       </c>
       <c r="D143" t="n">
-        <v>6.0</v>
+        <v>2914.0</v>
       </c>
       <c r="E143" t="n">
-        <v>6.0</v>
+        <v>3146.0</v>
       </c>
       <c r="F143" t="n">
-        <v>6.0</v>
+        <v>2303.0</v>
       </c>
       <c r="G143" t="n">
-        <v>6.0</v>
+        <v>2239.0</v>
       </c>
     </row>
     <row r="144">
@@ -4215,22 +3861,22 @@
         <v>148</v>
       </c>
       <c r="B144" t="n">
-        <v>25.0</v>
+        <v>161.0</v>
       </c>
       <c r="C144" t="n">
-        <v>6.0</v>
+        <v>97.0</v>
       </c>
       <c r="D144" t="n">
-        <v>1.0</v>
+        <v>2340.0</v>
       </c>
       <c r="E144" t="n">
-        <v>1.0</v>
+        <v>2335.0</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0</v>
+        <v>2082.0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0</v>
+        <v>1987.0</v>
       </c>
     </row>
     <row r="145">
@@ -4238,22 +3884,22 @@
         <v>149</v>
       </c>
       <c r="B145" t="n">
-        <v>207.0</v>
+        <v>3510.0</v>
       </c>
       <c r="C145" t="n">
-        <v>12.0</v>
+        <v>3085.0</v>
       </c>
       <c r="D145" t="n">
-        <v>1.0</v>
+        <v>1953.0</v>
       </c>
       <c r="E145" t="n">
-        <v>3.0</v>
+        <v>1977.0</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0</v>
+        <v>1759.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="146">
@@ -4261,22 +3907,22 @@
         <v>150</v>
       </c>
       <c r="B146" t="n">
-        <v>39.0</v>
+        <v>4154.0</v>
       </c>
       <c r="C146" t="n">
-        <v>6.0</v>
+        <v>3720.0</v>
       </c>
       <c r="D146" t="n">
-        <v>1.0</v>
+        <v>3600.0</v>
       </c>
       <c r="E146" t="n">
-        <v>1.0</v>
+        <v>4016.0</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0</v>
+        <v>3115.0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0</v>
+        <v>2908.0</v>
       </c>
     </row>
     <row r="147">
@@ -4284,22 +3930,22 @@
         <v>151</v>
       </c>
       <c r="B147" t="n">
-        <v>22.0</v>
+        <v>3452.0</v>
       </c>
       <c r="C147" t="n">
-        <v>9.0</v>
+        <v>2603.0</v>
       </c>
       <c r="D147" t="n">
-        <v>49.0</v>
+        <v>3626.0</v>
       </c>
       <c r="E147" t="n">
-        <v>95.0</v>
+        <v>3637.0</v>
       </c>
       <c r="F147" t="n">
-        <v>45.0</v>
+        <v>2769.0</v>
       </c>
       <c r="G147" t="n">
-        <v>44.0</v>
+        <v>2710.0</v>
       </c>
     </row>
     <row r="148">
@@ -4307,22 +3953,22 @@
         <v>152</v>
       </c>
       <c r="B148" t="n">
-        <v>26.0</v>
+        <v>3267.0</v>
       </c>
       <c r="C148" t="n">
-        <v>22.0</v>
+        <v>2183.0</v>
       </c>
       <c r="D148" t="n">
-        <v>1.0</v>
+        <v>2588.0</v>
       </c>
       <c r="E148" t="n">
-        <v>2.0</v>
+        <v>2616.0</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0</v>
+        <v>2246.0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0</v>
+        <v>2246.0</v>
       </c>
     </row>
     <row r="149">
@@ -4330,22 +3976,22 @@
         <v>153</v>
       </c>
       <c r="B149" t="n">
-        <v>26.0</v>
+        <v>4542.0</v>
       </c>
       <c r="C149" t="n">
-        <v>9.0</v>
+        <v>4150.0</v>
       </c>
       <c r="D149" t="n">
-        <v>12586.0</v>
+        <v>2861.0</v>
       </c>
       <c r="E149" t="n">
-        <v>14081.0</v>
+        <v>2887.0</v>
       </c>
       <c r="F149" t="n">
-        <v>92.0</v>
+        <v>2274.0</v>
       </c>
       <c r="G149" t="n">
-        <v>92.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="150">
@@ -4353,22 +3999,22 @@
         <v>154</v>
       </c>
       <c r="B150" t="n">
-        <v>6.0</v>
+        <v>3973.0</v>
       </c>
       <c r="C150" t="n">
-        <v>4.0</v>
+        <v>3659.0</v>
       </c>
       <c r="D150" t="n">
-        <v>18.0</v>
+        <v>39.0</v>
       </c>
       <c r="E150" t="n">
-        <v>15.0</v>
+        <v>60.0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="151">
@@ -4376,22 +4022,22 @@
         <v>155</v>
       </c>
       <c r="B151" t="n">
-        <v>11.0</v>
+        <v>3748.0</v>
       </c>
       <c r="C151" t="n">
-        <v>3.0</v>
+        <v>3209.0</v>
       </c>
       <c r="D151" t="n">
-        <v>1.0</v>
+        <v>2809.0</v>
       </c>
       <c r="E151" t="n">
-        <v>1.0</v>
+        <v>2791.0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0</v>
+        <v>2068.0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0</v>
+        <v>1950.0</v>
       </c>
     </row>
     <row r="152">
@@ -4399,22 +4045,22 @@
         <v>156</v>
       </c>
       <c r="B152" t="n">
-        <v>275.0</v>
+        <v>3394.0</v>
       </c>
       <c r="C152" t="n">
-        <v>134.0</v>
+        <v>2921.0</v>
       </c>
       <c r="D152" t="n">
-        <v>7.0</v>
+        <v>3787.0</v>
       </c>
       <c r="E152" t="n">
-        <v>3.0</v>
+        <v>3816.0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0</v>
+        <v>2959.0</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0</v>
+        <v>2811.0</v>
       </c>
     </row>
     <row r="153">
@@ -4422,22 +4068,22 @@
         <v>157</v>
       </c>
       <c r="B153" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="C153" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="D153" t="n">
         <v>32.0</v>
       </c>
-      <c r="C153" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1.0</v>
-      </c>
       <c r="E153" t="n">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="154">
@@ -4445,22 +4091,22 @@
         <v>158</v>
       </c>
       <c r="B154" t="n">
-        <v>17237.0</v>
+        <v>3110.0</v>
       </c>
       <c r="C154" t="n">
-        <v>14812.0</v>
+        <v>2839.0</v>
       </c>
       <c r="D154" t="n">
-        <v>1.0</v>
+        <v>2999.0</v>
       </c>
       <c r="E154" t="n">
-        <v>1.0</v>
+        <v>3041.0</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0</v>
+        <v>2208.0</v>
       </c>
       <c r="G154" t="n">
-        <v>1.0</v>
+        <v>2118.0</v>
       </c>
     </row>
     <row r="155">
@@ -4468,22 +4114,22 @@
         <v>159</v>
       </c>
       <c r="B155" t="n">
-        <v>87.0</v>
+        <v>4288.0</v>
       </c>
       <c r="C155" t="n">
-        <v>52.0</v>
+        <v>3834.0</v>
       </c>
       <c r="D155" t="n">
-        <v>1.0</v>
+        <v>3295.0</v>
       </c>
       <c r="E155" t="n">
-        <v>4.0</v>
+        <v>3288.0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0</v>
+        <v>2434.0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0</v>
+        <v>2289.0</v>
       </c>
     </row>
     <row r="156">
@@ -4491,22 +4137,22 @@
         <v>160</v>
       </c>
       <c r="B156" t="n">
-        <v>54.0</v>
+        <v>454.0</v>
       </c>
       <c r="C156" t="n">
-        <v>3.0</v>
+        <v>72.0</v>
       </c>
       <c r="D156" t="n">
-        <v>5.0</v>
+        <v>95.0</v>
       </c>
       <c r="E156" t="n">
-        <v>17.0</v>
+        <v>107.0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="157">
@@ -4514,22 +4160,22 @@
         <v>161</v>
       </c>
       <c r="B157" t="n">
-        <v>51.0</v>
+        <v>3249.0</v>
       </c>
       <c r="C157" t="n">
-        <v>19.0</v>
+        <v>3046.0</v>
       </c>
       <c r="D157" t="n">
-        <v>1.0</v>
+        <v>1757.0</v>
       </c>
       <c r="E157" t="n">
-        <v>1.0</v>
+        <v>1782.0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0</v>
+        <v>1447.0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="158">
@@ -4537,22 +4183,22 @@
         <v>162</v>
       </c>
       <c r="B158" t="n">
-        <v>142.0</v>
+        <v>3502.0</v>
       </c>
       <c r="C158" t="n">
-        <v>6.0</v>
+        <v>3310.0</v>
       </c>
       <c r="D158" t="n">
-        <v>1.0</v>
+        <v>1130.0</v>
       </c>
       <c r="E158" t="n">
-        <v>1.0</v>
+        <v>1201.0</v>
       </c>
       <c r="F158" t="n">
-        <v>1.0</v>
+        <v>725.0</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0</v>
+        <v>725.0</v>
       </c>
     </row>
     <row r="159">
@@ -4560,22 +4206,22 @@
         <v>163</v>
       </c>
       <c r="B159" t="n">
-        <v>34.0</v>
+        <v>161.0</v>
       </c>
       <c r="C159" t="n">
-        <v>3.0</v>
+        <v>131.0</v>
       </c>
       <c r="D159" t="n">
-        <v>1.0</v>
+        <v>2987.0</v>
       </c>
       <c r="E159" t="n">
-        <v>1.0</v>
+        <v>3017.0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0</v>
+        <v>2304.0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0</v>
+        <v>1841.0</v>
       </c>
     </row>
     <row r="160">
@@ -4583,22 +4229,22 @@
         <v>164</v>
       </c>
       <c r="B160" t="n">
-        <v>23.0</v>
+        <v>3235.0</v>
       </c>
       <c r="C160" t="n">
-        <v>14.0</v>
+        <v>1787.0</v>
       </c>
       <c r="D160" t="n">
-        <v>1837.0</v>
+        <v>2733.0</v>
       </c>
       <c r="E160" t="n">
-        <v>2826.0</v>
+        <v>2774.0</v>
       </c>
       <c r="F160" t="n">
-        <v>878.0</v>
+        <v>2341.0</v>
       </c>
       <c r="G160" t="n">
-        <v>554.0</v>
+        <v>2314.0</v>
       </c>
     </row>
     <row r="161">
@@ -4606,22 +4252,22 @@
         <v>165</v>
       </c>
       <c r="B161" t="n">
-        <v>116.0</v>
+        <v>2382.0</v>
       </c>
       <c r="C161" t="n">
-        <v>47.0</v>
+        <v>1483.0</v>
       </c>
       <c r="D161" t="n">
-        <v>1.0</v>
+        <v>1283.0</v>
       </c>
       <c r="E161" t="n">
-        <v>1.0</v>
+        <v>1308.0</v>
       </c>
       <c r="F161" t="n">
-        <v>1.0</v>
+        <v>1102.0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.0</v>
+        <v>1071.0</v>
       </c>
     </row>
     <row r="162">
@@ -4629,22 +4275,22 @@
         <v>166</v>
       </c>
       <c r="B162" t="n">
-        <v>11.0</v>
+        <v>3262.0</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0</v>
+        <v>3028.0</v>
       </c>
       <c r="D162" t="n">
-        <v>1.0</v>
+        <v>196.0</v>
       </c>
       <c r="E162" t="n">
-        <v>1.0</v>
+        <v>192.0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0</v>
+        <v>177.0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="163">
@@ -4652,22 +4298,22 @@
         <v>167</v>
       </c>
       <c r="B163" t="n">
-        <v>24.0</v>
+        <v>3864.0</v>
       </c>
       <c r="C163" t="n">
-        <v>6.0</v>
+        <v>3410.0</v>
       </c>
       <c r="D163" t="n">
-        <v>1.0</v>
+        <v>19339.0</v>
       </c>
       <c r="E163" t="n">
-        <v>1.0</v>
+        <v>19384.0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0</v>
+        <v>18851.0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0</v>
+        <v>18851.0</v>
       </c>
     </row>
     <row r="164">
@@ -4675,22 +4321,22 @@
         <v>168</v>
       </c>
       <c r="B164" t="n">
-        <v>123.0</v>
+        <v>3171.0</v>
       </c>
       <c r="C164" t="n">
-        <v>6.0</v>
+        <v>1311.0</v>
       </c>
       <c r="D164" t="n">
-        <v>1.0</v>
+        <v>13326.0</v>
       </c>
       <c r="E164" t="n">
-        <v>1.0</v>
+        <v>13424.0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0</v>
+        <v>12831.0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0</v>
+        <v>12831.0</v>
       </c>
     </row>
     <row r="165">
@@ -4698,2736 +4344,22 @@
         <v>169</v>
       </c>
       <c r="B165" t="n">
-        <v>148.0</v>
+        <v>352.0</v>
       </c>
       <c r="C165" t="n">
-        <v>5.0</v>
+        <v>241.0</v>
       </c>
       <c r="D165" t="n">
-        <v>1.0</v>
+        <v>20218.0</v>
       </c>
       <c r="E165" t="n">
-        <v>1.0</v>
+        <v>20256.0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0</v>
+        <v>19741.0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>170</v>
-      </c>
-      <c r="B166" t="n">
-        <v>111870.0</v>
-      </c>
-      <c r="C166" t="n">
-        <v>3259.0</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E166" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>171</v>
-      </c>
-      <c r="B167" t="n">
-        <v>154.0</v>
-      </c>
-      <c r="C167" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E167" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>172</v>
-      </c>
-      <c r="B168" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="C168" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D168" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E168" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>173</v>
-      </c>
-      <c r="B169" t="n">
-        <v>165.0</v>
-      </c>
-      <c r="C169" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E169" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>174</v>
-      </c>
-      <c r="B170" t="n">
-        <v>149.0</v>
-      </c>
-      <c r="C170" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D170" t="n">
-        <v>2757.0</v>
-      </c>
-      <c r="E170" t="n">
-        <v>2806.0</v>
-      </c>
-      <c r="F170" t="n">
-        <v>2116.0</v>
-      </c>
-      <c r="G170" t="n">
-        <v>2079.0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>175</v>
-      </c>
-      <c r="B171" t="n">
-        <v>105.0</v>
-      </c>
-      <c r="C171" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D171" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>176</v>
-      </c>
-      <c r="B172" t="n">
-        <v>148.0</v>
-      </c>
-      <c r="C172" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="D172" t="n">
-        <v>2419.0</v>
-      </c>
-      <c r="E172" t="n">
-        <v>3232.0</v>
-      </c>
-      <c r="F172" t="n">
-        <v>407.0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>354.0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>177</v>
-      </c>
-      <c r="B173" t="n">
-        <v>924.0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="D173" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="E173" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F173" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>178</v>
-      </c>
-      <c r="B174" t="n">
-        <v>123.0</v>
-      </c>
-      <c r="C174" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D174" t="n">
-        <v>3614.0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>3637.0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>3060.0</v>
-      </c>
-      <c r="G174" t="n">
-        <v>2916.0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>179</v>
-      </c>
-      <c r="B175" t="n">
-        <v>172.0</v>
-      </c>
-      <c r="C175" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>3004.0</v>
-      </c>
-      <c r="E175" t="n">
-        <v>3047.0</v>
-      </c>
-      <c r="F175" t="n">
-        <v>2385.0</v>
-      </c>
-      <c r="G175" t="n">
-        <v>2275.0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>180</v>
-      </c>
-      <c r="B176" t="n">
-        <v>3781.0</v>
-      </c>
-      <c r="C176" t="n">
-        <v>3357.0</v>
-      </c>
-      <c r="D176" t="n">
-        <v>863.0</v>
-      </c>
-      <c r="E176" t="n">
-        <v>911.0</v>
-      </c>
-      <c r="F176" t="n">
-        <v>705.0</v>
-      </c>
-      <c r="G176" t="n">
-        <v>689.0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>181</v>
-      </c>
-      <c r="B177" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="C177" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D177" t="n">
-        <v>636.0</v>
-      </c>
-      <c r="E177" t="n">
-        <v>647.0</v>
-      </c>
-      <c r="F177" t="n">
-        <v>502.0</v>
-      </c>
-      <c r="G177" t="n">
-        <v>480.0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>182</v>
-      </c>
-      <c r="B178" t="n">
-        <v>7903.0</v>
-      </c>
-      <c r="C178" t="n">
-        <v>3767.0</v>
-      </c>
-      <c r="D178" t="n">
-        <v>3225.0</v>
-      </c>
-      <c r="E178" t="n">
-        <v>3330.0</v>
-      </c>
-      <c r="F178" t="n">
-        <v>2874.0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>2656.0</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>183</v>
-      </c>
-      <c r="B179" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="C179" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="D179" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="E179" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F179" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>184</v>
-      </c>
-      <c r="B180" t="n">
-        <v>4753.0</v>
-      </c>
-      <c r="C180" t="n">
-        <v>4218.0</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E180" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>185</v>
-      </c>
-      <c r="B181" t="n">
-        <v>4210.0</v>
-      </c>
-      <c r="C181" t="n">
-        <v>3723.0</v>
-      </c>
-      <c r="D181" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>186</v>
-      </c>
-      <c r="B182" t="n">
-        <v>2758.0</v>
-      </c>
-      <c r="C182" t="n">
-        <v>1109.0</v>
-      </c>
-      <c r="D182" t="n">
-        <v>2439.0</v>
-      </c>
-      <c r="E182" t="n">
-        <v>2536.0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>2065.0</v>
-      </c>
-      <c r="G182" t="n">
-        <v>1999.0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>187</v>
-      </c>
-      <c r="B183" t="n">
-        <v>2382.0</v>
-      </c>
-      <c r="C183" t="n">
-        <v>818.0</v>
-      </c>
-      <c r="D183" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G183" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>188</v>
-      </c>
-      <c r="B184" t="n">
-        <v>4005.0</v>
-      </c>
-      <c r="C184" t="n">
-        <v>3590.0</v>
-      </c>
-      <c r="D184" t="n">
-        <v>1863.0</v>
-      </c>
-      <c r="E184" t="n">
-        <v>2181.0</v>
-      </c>
-      <c r="F184" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="G184" t="n">
-        <v>416.0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>189</v>
-      </c>
-      <c r="B185" t="n">
-        <v>106.0</v>
-      </c>
-      <c r="C185" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="E185" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="G185" t="n">
-        <v>74.0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>190</v>
-      </c>
-      <c r="B186" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="C186" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D186" t="n">
-        <v>4088.0</v>
-      </c>
-      <c r="E186" t="n">
-        <v>4162.0</v>
-      </c>
-      <c r="F186" t="n">
-        <v>3531.0</v>
-      </c>
-      <c r="G186" t="n">
-        <v>3223.0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>191</v>
-      </c>
-      <c r="B187" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="C187" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D187" t="n">
-        <v>2689.0</v>
-      </c>
-      <c r="E187" t="n">
-        <v>2761.0</v>
-      </c>
-      <c r="F187" t="n">
-        <v>2217.0</v>
-      </c>
-      <c r="G187" t="n">
-        <v>2131.0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>192</v>
-      </c>
-      <c r="B188" t="n">
-        <v>3577.0</v>
-      </c>
-      <c r="C188" t="n">
-        <v>3125.0</v>
-      </c>
-      <c r="D188" t="n">
-        <v>2239.0</v>
-      </c>
-      <c r="E188" t="n">
-        <v>2258.0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1858.0</v>
-      </c>
-      <c r="G188" t="n">
-        <v>1769.0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>193</v>
-      </c>
-      <c r="B189" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="C189" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D189" t="n">
-        <v>1157.0</v>
-      </c>
-      <c r="E189" t="n">
-        <v>1194.0</v>
-      </c>
-      <c r="F189" t="n">
-        <v>966.0</v>
-      </c>
-      <c r="G189" t="n">
-        <v>941.0</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>194</v>
-      </c>
-      <c r="B190" t="n">
-        <v>51228.0</v>
-      </c>
-      <c r="C190" t="n">
-        <v>2635.0</v>
-      </c>
-      <c r="D190" t="n">
-        <v>2804.0</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2853.0</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1930.0</v>
-      </c>
-      <c r="G190" t="n">
-        <v>1782.0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>195</v>
-      </c>
-      <c r="B191" t="n">
-        <v>695.0</v>
-      </c>
-      <c r="C191" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="D191" t="n">
-        <v>2606.0</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2630.0</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2103.0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2075.0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>196</v>
-      </c>
-      <c r="B192" t="n">
-        <v>4985.0</v>
-      </c>
-      <c r="C192" t="n">
-        <v>4550.0</v>
-      </c>
-      <c r="D192" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E192" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>197</v>
-      </c>
-      <c r="B193" t="n">
-        <v>3945.0</v>
-      </c>
-      <c r="C193" t="n">
-        <v>3384.0</v>
-      </c>
-      <c r="D193" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>198</v>
-      </c>
-      <c r="B194" t="n">
-        <v>3232.0</v>
-      </c>
-      <c r="C194" t="n">
-        <v>2631.0</v>
-      </c>
-      <c r="D194" t="n">
-        <v>2389.0</v>
-      </c>
-      <c r="E194" t="n">
-        <v>2496.0</v>
-      </c>
-      <c r="F194" t="n">
-        <v>1940.0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1861.0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>199</v>
-      </c>
-      <c r="B195" t="n">
-        <v>2806.0</v>
-      </c>
-      <c r="C195" t="n">
-        <v>1452.0</v>
-      </c>
-      <c r="D195" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>200</v>
-      </c>
-      <c r="B196" t="n">
-        <v>3692.0</v>
-      </c>
-      <c r="C196" t="n">
-        <v>3209.0</v>
-      </c>
-      <c r="D196" t="n">
-        <v>5064.0</v>
-      </c>
-      <c r="E196" t="n">
-        <v>6137.0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>241.0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>241.0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>201</v>
-      </c>
-      <c r="B197" t="n">
-        <v>3919.0</v>
-      </c>
-      <c r="C197" t="n">
-        <v>3266.0</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>202</v>
-      </c>
-      <c r="B198" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="C198" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="D198" t="n">
-        <v>2852.0</v>
-      </c>
-      <c r="E198" t="n">
-        <v>2836.0</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2350.0</v>
-      </c>
-      <c r="G198" t="n">
-        <v>2236.0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>203</v>
-      </c>
-      <c r="B199" t="n">
-        <v>542.0</v>
-      </c>
-      <c r="C199" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D199" t="n">
-        <v>2862.0</v>
-      </c>
-      <c r="E199" t="n">
-        <v>2943.0</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2400.0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>2344.0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>204</v>
-      </c>
-      <c r="B200" t="n">
-        <v>3465.0</v>
-      </c>
-      <c r="C200" t="n">
-        <v>3068.0</v>
-      </c>
-      <c r="D200" t="n">
-        <v>2471.0</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2632.0</v>
-      </c>
-      <c r="F200" t="n">
-        <v>2079.0</v>
-      </c>
-      <c r="G200" t="n">
-        <v>2025.0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>205</v>
-      </c>
-      <c r="B201" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="C201" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="D201" t="n">
-        <v>1172.0</v>
-      </c>
-      <c r="E201" t="n">
-        <v>1198.0</v>
-      </c>
-      <c r="F201" t="n">
-        <v>980.0</v>
-      </c>
-      <c r="G201" t="n">
-        <v>967.0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>206</v>
-      </c>
-      <c r="B202" t="n">
-        <v>7879.0</v>
-      </c>
-      <c r="C202" t="n">
-        <v>6873.0</v>
-      </c>
-      <c r="D202" t="n">
-        <v>2604.0</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2661.0</v>
-      </c>
-      <c r="F202" t="n">
-        <v>2224.0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>2046.0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>207</v>
-      </c>
-      <c r="B203" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="C203" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D203" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E203" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F203" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="s">
-        <v>208</v>
-      </c>
-      <c r="B204" t="n">
-        <v>3872.0</v>
-      </c>
-      <c r="C204" t="n">
-        <v>3407.0</v>
-      </c>
-      <c r="D204" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>209</v>
-      </c>
-      <c r="B205" t="n">
-        <v>3911.0</v>
-      </c>
-      <c r="C205" t="n">
-        <v>3482.0</v>
-      </c>
-      <c r="D205" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E205" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s">
-        <v>210</v>
-      </c>
-      <c r="B206" t="n">
-        <v>3656.0</v>
-      </c>
-      <c r="C206" t="n">
-        <v>3155.0</v>
-      </c>
-      <c r="D206" t="n">
-        <v>2388.0</v>
-      </c>
-      <c r="E206" t="n">
-        <v>2513.0</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1928.0</v>
-      </c>
-      <c r="G206" t="n">
-        <v>1906.0</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="s">
-        <v>211</v>
-      </c>
-      <c r="B207" t="n">
-        <v>2387.0</v>
-      </c>
-      <c r="C207" t="n">
-        <v>1386.0</v>
-      </c>
-      <c r="D207" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="s">
-        <v>212</v>
-      </c>
-      <c r="B208" t="n">
-        <v>3534.0</v>
-      </c>
-      <c r="C208" t="n">
-        <v>2992.0</v>
-      </c>
-      <c r="D208" t="n">
-        <v>8527.0</v>
-      </c>
-      <c r="E208" t="n">
-        <v>11090.0</v>
-      </c>
-      <c r="F208" t="n">
-        <v>2271.0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1461.0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="s">
-        <v>213</v>
-      </c>
-      <c r="B209" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="C209" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="D209" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>214</v>
-      </c>
-      <c r="B210" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="C210" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D210" t="n">
-        <v>2803.0</v>
-      </c>
-      <c r="E210" t="n">
-        <v>2815.0</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2218.0</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2163.0</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>215</v>
-      </c>
-      <c r="B211" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="C211" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D211" t="n">
-        <v>3210.0</v>
-      </c>
-      <c r="E211" t="n">
-        <v>3376.0</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2621.0</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2494.0</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>216</v>
-      </c>
-      <c r="B212" t="n">
-        <v>3529.0</v>
-      </c>
-      <c r="C212" t="n">
-        <v>3108.0</v>
-      </c>
-      <c r="D212" t="n">
-        <v>796.0</v>
-      </c>
-      <c r="E212" t="n">
-        <v>812.0</v>
-      </c>
-      <c r="F212" t="n">
-        <v>743.0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>725.0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>217</v>
-      </c>
-      <c r="B213" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="C213" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="D213" t="n">
-        <v>1044.0</v>
-      </c>
-      <c r="E213" t="n">
-        <v>1056.0</v>
-      </c>
-      <c r="F213" t="n">
-        <v>856.0</v>
-      </c>
-      <c r="G213" t="n">
-        <v>839.0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>218</v>
-      </c>
-      <c r="B214" t="n">
-        <v>13530.0</v>
-      </c>
-      <c r="C214" t="n">
-        <v>11905.0</v>
-      </c>
-      <c r="D214" t="n">
-        <v>3324.0</v>
-      </c>
-      <c r="E214" t="n">
-        <v>3443.0</v>
-      </c>
-      <c r="F214" t="n">
-        <v>2830.0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>2610.0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>219</v>
-      </c>
-      <c r="B215" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="C215" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="D215" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E215" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>220</v>
-      </c>
-      <c r="B216" t="n">
-        <v>3840.0</v>
-      </c>
-      <c r="C216" t="n">
-        <v>3385.0</v>
-      </c>
-      <c r="D216" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E216" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="s">
-        <v>221</v>
-      </c>
-      <c r="B217" t="n">
-        <v>4514.0</v>
-      </c>
-      <c r="C217" t="n">
-        <v>4005.0</v>
-      </c>
-      <c r="D217" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E217" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="s">
-        <v>222</v>
-      </c>
-      <c r="B218" t="n">
-        <v>2604.0</v>
-      </c>
-      <c r="C218" t="n">
-        <v>932.0</v>
-      </c>
-      <c r="D218" t="n">
-        <v>2495.0</v>
-      </c>
-      <c r="E218" t="n">
-        <v>2608.0</v>
-      </c>
-      <c r="F218" t="n">
-        <v>1957.0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>1892.0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="s">
-        <v>223</v>
-      </c>
-      <c r="B219" t="n">
-        <v>2475.0</v>
-      </c>
-      <c r="C219" t="n">
-        <v>1250.0</v>
-      </c>
-      <c r="D219" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E219" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F219" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="s">
-        <v>224</v>
-      </c>
-      <c r="B220" t="n">
-        <v>4021.0</v>
-      </c>
-      <c r="C220" t="n">
-        <v>3660.0</v>
-      </c>
-      <c r="D220" t="n">
-        <v>21152.0</v>
-      </c>
-      <c r="E220" t="n">
-        <v>23481.0</v>
-      </c>
-      <c r="F220" t="n">
-        <v>921.0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>756.0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="s">
-        <v>225</v>
-      </c>
-      <c r="B221" t="n">
-        <v>94.0</v>
-      </c>
-      <c r="C221" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="D221" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="E221" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F221" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>226</v>
-      </c>
-      <c r="B222" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="C222" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D222" t="n">
-        <v>2481.0</v>
-      </c>
-      <c r="E222" t="n">
-        <v>2556.0</v>
-      </c>
-      <c r="F222" t="n">
-        <v>2128.0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>2086.0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>227</v>
-      </c>
-      <c r="B223" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="C223" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D223" t="n">
-        <v>2865.0</v>
-      </c>
-      <c r="E223" t="n">
-        <v>3139.0</v>
-      </c>
-      <c r="F223" t="n">
-        <v>2239.0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>2168.0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>228</v>
-      </c>
-      <c r="B224" t="n">
-        <v>3586.0</v>
-      </c>
-      <c r="C224" t="n">
-        <v>3076.0</v>
-      </c>
-      <c r="D224" t="n">
-        <v>2324.0</v>
-      </c>
-      <c r="E224" t="n">
-        <v>2370.0</v>
-      </c>
-      <c r="F224" t="n">
-        <v>2049.0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>1949.0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>229</v>
-      </c>
-      <c r="B225" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="C225" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="D225" t="n">
-        <v>1934.0</v>
-      </c>
-      <c r="E225" t="n">
-        <v>1979.0</v>
-      </c>
-      <c r="F225" t="n">
-        <v>1725.0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>1616.0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>230</v>
-      </c>
-      <c r="B226" t="n">
-        <v>28323.0</v>
-      </c>
-      <c r="C226" t="n">
-        <v>24532.0</v>
-      </c>
-      <c r="D226" t="n">
-        <v>3592.0</v>
-      </c>
-      <c r="E226" t="n">
-        <v>3997.0</v>
-      </c>
-      <c r="F226" t="n">
-        <v>3034.0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>2796.0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>231</v>
-      </c>
-      <c r="B227" t="n">
-        <v>161.0</v>
-      </c>
-      <c r="C227" t="n">
-        <v>97.0</v>
-      </c>
-      <c r="D227" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E227" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>232</v>
-      </c>
-      <c r="B228" t="n">
-        <v>3510.0</v>
-      </c>
-      <c r="C228" t="n">
-        <v>3085.0</v>
-      </c>
-      <c r="D228" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E228" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>233</v>
-      </c>
-      <c r="B229" t="n">
-        <v>4154.0</v>
-      </c>
-      <c r="C229" t="n">
-        <v>3720.0</v>
-      </c>
-      <c r="D229" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E229" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>234</v>
-      </c>
-      <c r="B230" t="n">
-        <v>3452.0</v>
-      </c>
-      <c r="C230" t="n">
-        <v>2603.0</v>
-      </c>
-      <c r="D230" t="n">
-        <v>3552.0</v>
-      </c>
-      <c r="E230" t="n">
-        <v>3627.0</v>
-      </c>
-      <c r="F230" t="n">
-        <v>2661.0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>2615.0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>235</v>
-      </c>
-      <c r="B231" t="n">
-        <v>3267.0</v>
-      </c>
-      <c r="C231" t="n">
-        <v>2183.0</v>
-      </c>
-      <c r="D231" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="E231" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F231" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="s">
-        <v>236</v>
-      </c>
-      <c r="B232" t="n">
-        <v>4542.0</v>
-      </c>
-      <c r="C232" t="n">
-        <v>4150.0</v>
-      </c>
-      <c r="D232" t="n">
-        <v>507.0</v>
-      </c>
-      <c r="E232" t="n">
-        <v>600.0</v>
-      </c>
-      <c r="F232" t="n">
-        <v>449.0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>449.0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="s">
-        <v>237</v>
-      </c>
-      <c r="B233" t="n">
-        <v>223.0</v>
-      </c>
-      <c r="C233" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="D233" t="n">
-        <v>2550.0</v>
-      </c>
-      <c r="E233" t="n">
-        <v>2602.0</v>
-      </c>
-      <c r="F233" t="n">
-        <v>2177.0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>2162.0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s">
-        <v>238</v>
-      </c>
-      <c r="B234" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="C234" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D234" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="E234" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="F234" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>22.0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="s">
-        <v>239</v>
-      </c>
-      <c r="B235" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="C235" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D235" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="E235" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F235" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
-        <v>240</v>
-      </c>
-      <c r="B236" t="n">
-        <v>3973.0</v>
-      </c>
-      <c r="C236" t="n">
-        <v>3659.0</v>
-      </c>
-      <c r="D236" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="E236" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="F236" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s">
-        <v>241</v>
-      </c>
-      <c r="B237" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="C237" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="D237" t="n">
-        <v>2838.0</v>
-      </c>
-      <c r="E237" t="n">
-        <v>2855.0</v>
-      </c>
-      <c r="F237" t="n">
-        <v>2203.0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>2076.0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s">
-        <v>242</v>
-      </c>
-      <c r="B238" t="n">
-        <v>1209.0</v>
-      </c>
-      <c r="C238" t="n">
-        <v>829.0</v>
-      </c>
-      <c r="D238" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="E238" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="F238" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>26.0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s">
-        <v>243</v>
-      </c>
-      <c r="B239" t="n">
-        <v>3748.0</v>
-      </c>
-      <c r="C239" t="n">
-        <v>3209.0</v>
-      </c>
-      <c r="D239" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E239" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F239" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s">
-        <v>244</v>
-      </c>
-      <c r="B240" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="C240" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="D240" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E240" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F240" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s">
-        <v>245</v>
-      </c>
-      <c r="B241" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="C241" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="D241" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E241" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s">
-        <v>246</v>
-      </c>
-      <c r="B242" t="n">
-        <v>81.0</v>
-      </c>
-      <c r="C242" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="D242" t="n">
-        <v>2770.0</v>
-      </c>
-      <c r="E242" t="n">
-        <v>2813.0</v>
-      </c>
-      <c r="F242" t="n">
-        <v>1994.0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>1869.0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s">
-        <v>247</v>
-      </c>
-      <c r="B243" t="n">
-        <v>3394.0</v>
-      </c>
-      <c r="C243" t="n">
-        <v>2921.0</v>
-      </c>
-      <c r="D243" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E243" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F243" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s">
-        <v>248</v>
-      </c>
-      <c r="B244" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="C244" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="D244" t="n">
-        <v>4198.0</v>
-      </c>
-      <c r="E244" t="n">
-        <v>5115.0</v>
-      </c>
-      <c r="F244" t="n">
-        <v>404.0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>366.0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s">
-        <v>249</v>
-      </c>
-      <c r="B245" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="C245" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="D245" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E245" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F245" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G245" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s">
-        <v>250</v>
-      </c>
-      <c r="B246" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="C246" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="D246" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E246" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F246" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G246" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s">
-        <v>251</v>
-      </c>
-      <c r="B247" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="C247" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="D247" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E247" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F247" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s">
-        <v>252</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3110.0</v>
-      </c>
-      <c r="C248" t="n">
-        <v>2839.0</v>
-      </c>
-      <c r="D248" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E248" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F248" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s">
-        <v>253</v>
-      </c>
-      <c r="B249" t="n">
-        <v>146.0</v>
-      </c>
-      <c r="C249" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D249" t="n">
-        <v>3767.0</v>
-      </c>
-      <c r="E249" t="n">
-        <v>3767.0</v>
-      </c>
-      <c r="F249" t="n">
-        <v>2847.0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>2709.0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s">
-        <v>254</v>
-      </c>
-      <c r="B250" t="n">
-        <v>140583.0</v>
-      </c>
-      <c r="C250" t="n">
-        <v>5497.0</v>
-      </c>
-      <c r="D250" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="E250" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="F250" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>29.0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="s">
-        <v>255</v>
-      </c>
-      <c r="B251" t="n">
-        <v>175.0</v>
-      </c>
-      <c r="C251" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="D251" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E251" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F251" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s">
-        <v>256</v>
-      </c>
-      <c r="B252" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="C252" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D252" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E252" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F252" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>257</v>
-      </c>
-      <c r="B253" t="n">
-        <v>218.0</v>
-      </c>
-      <c r="C253" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D253" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E253" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F253" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>258</v>
-      </c>
-      <c r="B254" t="n">
-        <v>116.0</v>
-      </c>
-      <c r="C254" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D254" t="n">
-        <v>2978.0</v>
-      </c>
-      <c r="E254" t="n">
-        <v>3041.0</v>
-      </c>
-      <c r="F254" t="n">
-        <v>2170.0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>2046.0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>259</v>
-      </c>
-      <c r="B255" t="n">
-        <v>4288.0</v>
-      </c>
-      <c r="C255" t="n">
-        <v>3834.0</v>
-      </c>
-      <c r="D255" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="E255" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="F255" t="n">
-        <v>228.0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>203.0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>260</v>
-      </c>
-      <c r="B256" t="n">
-        <v>454.0</v>
-      </c>
-      <c r="C256" t="n">
-        <v>72.0</v>
-      </c>
-      <c r="D256" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E256" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F256" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>261</v>
-      </c>
-      <c r="B257" t="n">
-        <v>243.0</v>
-      </c>
-      <c r="C257" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="D257" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E257" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F257" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>262</v>
-      </c>
-      <c r="B258" t="n">
-        <v>161.0</v>
-      </c>
-      <c r="C258" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D258" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E258" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F258" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>263</v>
-      </c>
-      <c r="B259" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="C259" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D259" t="n">
-        <v>3239.0</v>
-      </c>
-      <c r="E259" t="n">
-        <v>3307.0</v>
-      </c>
-      <c r="F259" t="n">
-        <v>2372.0</v>
-      </c>
-      <c r="G259" t="n">
-        <v>2228.0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>264</v>
-      </c>
-      <c r="B260" t="n">
-        <v>3249.0</v>
-      </c>
-      <c r="C260" t="n">
-        <v>3046.0</v>
-      </c>
-      <c r="D260" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="E260" t="n">
-        <v>107.0</v>
-      </c>
-      <c r="F260" t="n">
-        <v>66.0</v>
-      </c>
-      <c r="G260" t="n">
-        <v>66.0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>265</v>
-      </c>
-      <c r="B261" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C261" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D261" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E261" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F261" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>266</v>
-      </c>
-      <c r="B262" t="n">
-        <v>1004.0</v>
-      </c>
-      <c r="C262" t="n">
-        <v>299.0</v>
-      </c>
-      <c r="D262" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E262" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F262" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>267</v>
-      </c>
-      <c r="B263" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C263" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D263" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E263" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F263" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s">
-        <v>268</v>
-      </c>
-      <c r="B264" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C264" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D264" t="n">
-        <v>1771.0</v>
-      </c>
-      <c r="E264" t="n">
-        <v>1782.0</v>
-      </c>
-      <c r="F264" t="n">
-        <v>1439.0</v>
-      </c>
-      <c r="G264" t="n">
-        <v>1376.0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s">
-        <v>269</v>
-      </c>
-      <c r="B265" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C265" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D265" t="n">
-        <v>1096.0</v>
-      </c>
-      <c r="E265" t="n">
-        <v>1204.0</v>
-      </c>
-      <c r="F265" t="n">
-        <v>699.0</v>
-      </c>
-      <c r="G265" t="n">
-        <v>694.0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s">
-        <v>270</v>
-      </c>
-      <c r="B266" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="C266" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D266" t="n">
-        <v>2969.0</v>
-      </c>
-      <c r="E266" t="n">
-        <v>3017.0</v>
-      </c>
-      <c r="F266" t="n">
-        <v>2267.0</v>
-      </c>
-      <c r="G266" t="n">
-        <v>1802.0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="s">
-        <v>271</v>
-      </c>
-      <c r="B267" t="n">
-        <v>3502.0</v>
-      </c>
-      <c r="C267" t="n">
-        <v>3310.0</v>
-      </c>
-      <c r="D267" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E267" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F267" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G267" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="s">
-        <v>272</v>
-      </c>
-      <c r="B268" t="n">
-        <v>161.0</v>
-      </c>
-      <c r="C268" t="n">
-        <v>131.0</v>
-      </c>
-      <c r="D268" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E268" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F268" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="s">
-        <v>273</v>
-      </c>
-      <c r="B269" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="C269" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D269" t="n">
-        <v>2710.0</v>
-      </c>
-      <c r="E269" t="n">
-        <v>2770.0</v>
-      </c>
-      <c r="F269" t="n">
-        <v>2309.0</v>
-      </c>
-      <c r="G269" t="n">
-        <v>2251.0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="s">
-        <v>274</v>
-      </c>
-      <c r="B270" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C270" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D270" t="n">
-        <v>1293.0</v>
-      </c>
-      <c r="E270" t="n">
-        <v>1308.0</v>
-      </c>
-      <c r="F270" t="n">
-        <v>1110.0</v>
-      </c>
-      <c r="G270" t="n">
-        <v>1062.0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s">
-        <v>275</v>
-      </c>
-      <c r="B271" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="C271" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D271" t="n">
-        <v>192.0</v>
-      </c>
-      <c r="E271" t="n">
-        <v>192.0</v>
-      </c>
-      <c r="F271" t="n">
-        <v>173.0</v>
-      </c>
-      <c r="G271" t="n">
-        <v>173.0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="s">
-        <v>276</v>
-      </c>
-      <c r="B272" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="C272" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D272" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E272" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F272" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G272" t="n">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="s">
-        <v>277</v>
-      </c>
-      <c r="B273" t="n">
-        <v>3235.0</v>
-      </c>
-      <c r="C273" t="n">
-        <v>1787.0</v>
-      </c>
-      <c r="D273" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F273" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="s">
-        <v>278</v>
-      </c>
-      <c r="B274" t="n">
-        <v>2382.0</v>
-      </c>
-      <c r="C274" t="n">
-        <v>1483.0</v>
-      </c>
-      <c r="D274" t="n">
-        <v>19339.0</v>
-      </c>
-      <c r="E274" t="n">
-        <v>19384.0</v>
-      </c>
-      <c r="F274" t="n">
-        <v>18851.0</v>
-      </c>
-      <c r="G274" t="n">
-        <v>18851.0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="s">
-        <v>279</v>
-      </c>
-      <c r="B275" t="n">
-        <v>3262.0</v>
-      </c>
-      <c r="C275" t="n">
-        <v>3028.0</v>
-      </c>
-      <c r="D275" t="n">
-        <v>13326.0</v>
-      </c>
-      <c r="E275" t="n">
-        <v>13424.0</v>
-      </c>
-      <c r="F275" t="n">
-        <v>12831.0</v>
-      </c>
-      <c r="G275" t="n">
-        <v>12831.0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="s">
-        <v>280</v>
-      </c>
-      <c r="B276" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="C276" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D276" t="n">
-        <v>20218.0</v>
-      </c>
-      <c r="E276" t="n">
-        <v>20256.0</v>
-      </c>
-      <c r="F276" t="n">
         <v>19741.0</v>
-      </c>
-      <c r="G276" t="n">
-        <v>19741.0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="s">
-        <v>281</v>
-      </c>
-      <c r="B277" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="C277" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D277" t="n">
-        <v>17598.0</v>
-      </c>
-      <c r="E277" t="n">
-        <v>17690.0</v>
-      </c>
-      <c r="F277" t="n">
-        <v>17150.0</v>
-      </c>
-      <c r="G277" t="n">
-        <v>17150.0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s">
-        <v>282</v>
-      </c>
-      <c r="B278" t="n">
-        <v>3864.0</v>
-      </c>
-      <c r="C278" t="n">
-        <v>3410.0</v>
-      </c>
-      <c r="D278" t="n">
-        <v>20130.0</v>
-      </c>
-      <c r="E278" t="n">
-        <v>20167.0</v>
-      </c>
-      <c r="F278" t="n">
-        <v>19412.0</v>
-      </c>
-      <c r="G278" t="n">
-        <v>19412.0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="s">
-        <v>283</v>
-      </c>
-      <c r="B279" t="n">
-        <v>3171.0</v>
-      </c>
-      <c r="C279" t="n">
-        <v>1311.0</v>
-      </c>
-      <c r="D279" t="n">
-        <v>17149.0</v>
-      </c>
-      <c r="E279" t="n">
-        <v>17187.0</v>
-      </c>
-      <c r="F279" t="n">
-        <v>16400.0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>16400.0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>284</v>
-      </c>
-      <c r="B280" t="n">
-        <v>352.0</v>
-      </c>
-      <c r="C280" t="n">
-        <v>241.0</v>
-      </c>
-      <c r="D280" t="n">
-        <v>24194.0</v>
-      </c>
-      <c r="E280" t="n">
-        <v>24367.0</v>
-      </c>
-      <c r="F280" t="n">
-        <v>23763.0</v>
-      </c>
-      <c r="G280" t="n">
-        <v>23763.0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s">
-        <v>285</v>
-      </c>
-      <c r="B281" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="C281" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D281" t="n">
-        <v>20624.0</v>
-      </c>
-      <c r="E281" t="n">
-        <v>20670.0</v>
-      </c>
-      <c r="F281" t="n">
-        <v>20191.0</v>
-      </c>
-      <c r="G281" t="n">
-        <v>20191.0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s">
-        <v>286</v>
-      </c>
-      <c r="B282" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C282" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D282" t="n">
-        <v>20099.0</v>
-      </c>
-      <c r="E282" t="n">
-        <v>20252.0</v>
-      </c>
-      <c r="F282" t="n">
-        <v>19674.0</v>
-      </c>
-      <c r="G282" t="n">
-        <v>19674.0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s">
-        <v>287</v>
-      </c>
-      <c r="B283" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C283" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D283" t="n">
-        <v>117957.0</v>
-      </c>
-      <c r="E283" t="n">
-        <v>120930.0</v>
-      </c>
-      <c r="F283" t="n">
-        <v>115506.0</v>
-      </c>
-      <c r="G283" t="n">
-        <v>115292.0</v>
       </c>
     </row>
   </sheetData>
